--- a/output/cluster_review_edits.xlsx
+++ b/output/cluster_review_edits.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilya/spatial-queries/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F652DCFF-CBEC-F04D-B1C3-D66CE8A15177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A4460B-3118-6749-82E5-D09FE017C545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="235">
   <si>
     <t>label</t>
   </si>
@@ -713,6 +713,18 @@
   </si>
   <si>
     <t>Generic factual queries</t>
+  </si>
+  <si>
+    <t>Distance and proximity</t>
+  </si>
+  <si>
+    <t>Occurrence</t>
+  </si>
+  <si>
+    <t>Temporal</t>
+  </si>
+  <si>
+    <t>group</t>
   </si>
 </sst>
 </file>
@@ -742,7 +754,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -758,6 +770,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -813,6 +831,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1123,7 +1145,7 @@
     <col min="5" max="5" width="67.83203125" customWidth="1"/>
     <col min="6" max="6" width="23.83203125" customWidth="1"/>
     <col min="7" max="7" width="23.33203125" customWidth="1"/>
-    <col min="8" max="8" width="3.5" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="53.6640625" customWidth="1"/>
     <col min="10" max="10" width="37.33203125" customWidth="1"/>
   </cols>
@@ -1150,6 +1172,9 @@
       <c r="G1" s="2" t="s">
         <v>79</v>
       </c>
+      <c r="H1" s="6" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
@@ -1173,6 +1198,9 @@
       <c r="G2" t="s">
         <v>162</v>
       </c>
+      <c r="H2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -1196,6 +1224,9 @@
       <c r="G3" t="s">
         <v>165</v>
       </c>
+      <c r="H3" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -1219,6 +1250,9 @@
       <c r="G4" t="s">
         <v>163</v>
       </c>
+      <c r="H4" t="s">
+        <v>155</v>
+      </c>
       <c r="I4" s="4" t="s">
         <v>212</v>
       </c>
@@ -1245,6 +1279,9 @@
       <c r="G5" t="s">
         <v>161</v>
       </c>
+      <c r="H5" t="s">
+        <v>155</v>
+      </c>
       <c r="I5" s="4" t="s">
         <v>213</v>
       </c>
@@ -1271,6 +1308,9 @@
       <c r="G6" t="s">
         <v>162</v>
       </c>
+      <c r="H6" t="s">
+        <v>156</v>
+      </c>
       <c r="I6" s="4" t="s">
         <v>214</v>
       </c>
@@ -1297,6 +1337,9 @@
       <c r="G7" t="s">
         <v>162</v>
       </c>
+      <c r="H7" t="s">
+        <v>156</v>
+      </c>
       <c r="I7" s="4" t="s">
         <v>215</v>
       </c>
@@ -1323,6 +1366,9 @@
       <c r="G8" t="s">
         <v>162</v>
       </c>
+      <c r="H8" t="s">
+        <v>156</v>
+      </c>
       <c r="I8" s="4" t="s">
         <v>216</v>
       </c>
@@ -1349,6 +1395,9 @@
       <c r="G9" t="s">
         <v>162</v>
       </c>
+      <c r="H9" t="s">
+        <v>156</v>
+      </c>
       <c r="I9" s="4" t="s">
         <v>225</v>
       </c>
@@ -1375,6 +1424,9 @@
       <c r="G10" t="s">
         <v>162</v>
       </c>
+      <c r="H10" t="s">
+        <v>156</v>
+      </c>
       <c r="I10" s="4" t="s">
         <v>227</v>
       </c>
@@ -1401,6 +1453,9 @@
       <c r="G11" t="s">
         <v>162</v>
       </c>
+      <c r="H11" t="s">
+        <v>156</v>
+      </c>
       <c r="I11" s="4" t="s">
         <v>226</v>
       </c>
@@ -1427,6 +1482,9 @@
       <c r="G12" t="s">
         <v>162</v>
       </c>
+      <c r="H12" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -1450,6 +1508,9 @@
       <c r="G13" t="s">
         <v>162</v>
       </c>
+      <c r="H13" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -1473,6 +1534,9 @@
       <c r="G14" t="s">
         <v>162</v>
       </c>
+      <c r="H14" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -1496,6 +1560,9 @@
       <c r="G15" t="s">
         <v>162</v>
       </c>
+      <c r="H15" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -1519,6 +1586,9 @@
       <c r="G16" t="s">
         <v>162</v>
       </c>
+      <c r="H16" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
@@ -1542,6 +1612,9 @@
       <c r="G17" t="s">
         <v>162</v>
       </c>
+      <c r="H17" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
@@ -1565,6 +1638,9 @@
       <c r="G18" t="s">
         <v>162</v>
       </c>
+      <c r="H18" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
@@ -1588,6 +1664,9 @@
       <c r="G19" t="s">
         <v>162</v>
       </c>
+      <c r="H19" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
@@ -1611,6 +1690,9 @@
       <c r="G20" t="s">
         <v>162</v>
       </c>
+      <c r="H20" t="s">
+        <v>156</v>
+      </c>
       <c r="I20" s="5" t="s">
         <v>217</v>
       </c>
@@ -1637,6 +1719,9 @@
       <c r="G21" t="s">
         <v>162</v>
       </c>
+      <c r="H21" t="s">
+        <v>156</v>
+      </c>
       <c r="I21" s="5" t="s">
         <v>218</v>
       </c>
@@ -1663,6 +1748,9 @@
       <c r="G22" t="s">
         <v>162</v>
       </c>
+      <c r="H22" t="s">
+        <v>156</v>
+      </c>
       <c r="I22" s="5" t="s">
         <v>219</v>
       </c>
@@ -1689,6 +1777,9 @@
       <c r="G23" t="s">
         <v>162</v>
       </c>
+      <c r="H23" t="s">
+        <v>156</v>
+      </c>
       <c r="I23" s="5" t="s">
         <v>220</v>
       </c>
@@ -1715,6 +1806,9 @@
       <c r="G24" t="s">
         <v>162</v>
       </c>
+      <c r="H24" t="s">
+        <v>156</v>
+      </c>
       <c r="I24" s="5" t="s">
         <v>228</v>
       </c>
@@ -1741,6 +1835,9 @@
       <c r="G25" t="s">
         <v>162</v>
       </c>
+      <c r="H25" t="s">
+        <v>156</v>
+      </c>
       <c r="I25" s="5" t="s">
         <v>221</v>
       </c>
@@ -1767,6 +1864,9 @@
       <c r="G26" t="s">
         <v>162</v>
       </c>
+      <c r="H26" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
@@ -1790,6 +1890,9 @@
       <c r="G27" t="s">
         <v>162</v>
       </c>
+      <c r="H27" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
@@ -1813,6 +1916,9 @@
       <c r="G28" t="s">
         <v>162</v>
       </c>
+      <c r="H28" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
@@ -1836,6 +1942,9 @@
       <c r="G29" t="s">
         <v>162</v>
       </c>
+      <c r="H29" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
@@ -1859,6 +1968,9 @@
       <c r="G30" t="s">
         <v>162</v>
       </c>
+      <c r="H30" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
@@ -1882,6 +1994,12 @@
       <c r="G31" t="s">
         <v>162</v>
       </c>
+      <c r="H31" t="s">
+        <v>231</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
@@ -1905,8 +2023,14 @@
       <c r="G32" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>231</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>67</v>
       </c>
@@ -1928,8 +2052,14 @@
       <c r="G33" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>231</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>4</v>
       </c>
@@ -1951,8 +2081,14 @@
       <c r="G34" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>231</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>20</v>
       </c>
@@ -1974,8 +2110,14 @@
       <c r="G35" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>155</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>69</v>
       </c>
@@ -1997,8 +2139,11 @@
       <c r="G36" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>-1</v>
       </c>
@@ -2015,7 +2160,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>56</v>
       </c>
@@ -2037,8 +2182,11 @@
       <c r="G38" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>63</v>
       </c>
@@ -2060,8 +2208,11 @@
       <c r="G39" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2</v>
       </c>
@@ -2083,8 +2234,11 @@
       <c r="G40" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>54</v>
       </c>
@@ -2106,8 +2260,11 @@
       <c r="G41" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>48</v>
       </c>
@@ -2129,8 +2286,11 @@
       <c r="G42" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>46</v>
       </c>
@@ -2152,8 +2312,11 @@
       <c r="G43" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>35</v>
       </c>
@@ -2175,8 +2338,11 @@
       <c r="G44" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>9</v>
       </c>
@@ -2198,8 +2364,11 @@
       <c r="G45" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>5</v>
       </c>
@@ -2221,8 +2390,11 @@
       <c r="G46" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>64</v>
       </c>
@@ -2244,8 +2416,11 @@
       <c r="G47" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -2267,8 +2442,11 @@
       <c r="G48" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>22</v>
       </c>
@@ -2290,8 +2468,11 @@
       <c r="G49" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>55</v>
       </c>
@@ -2313,8 +2494,11 @@
       <c r="G50" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>60</v>
       </c>
@@ -2336,8 +2520,11 @@
       <c r="G51" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>3</v>
       </c>
@@ -2359,8 +2546,11 @@
       <c r="G52" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>15</v>
       </c>
@@ -2382,8 +2572,11 @@
       <c r="G53" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>59</v>
       </c>
@@ -2405,8 +2598,11 @@
       <c r="G54" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>16</v>
       </c>
@@ -2428,8 +2624,11 @@
       <c r="G55" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>65</v>
       </c>
@@ -2451,8 +2650,11 @@
       <c r="G56" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -2474,8 +2676,11 @@
       <c r="G57" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>23</v>
       </c>
@@ -2497,8 +2702,11 @@
       <c r="G58" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>49</v>
       </c>
@@ -2520,8 +2728,11 @@
       <c r="G59" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>11</v>
       </c>
@@ -2543,8 +2754,11 @@
       <c r="G60" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>71</v>
       </c>
@@ -2566,8 +2780,11 @@
       <c r="G61" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>66</v>
       </c>
@@ -2589,8 +2806,11 @@
       <c r="G62" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>51</v>
       </c>
@@ -2612,8 +2832,11 @@
       <c r="G63" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>57</v>
       </c>
@@ -2635,8 +2858,11 @@
       <c r="G64" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>6</v>
       </c>
@@ -2658,8 +2884,11 @@
       <c r="G65" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>39</v>
       </c>
@@ -2681,8 +2910,11 @@
       <c r="G66" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>7</v>
       </c>
@@ -2704,8 +2936,11 @@
       <c r="G67" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>72</v>
       </c>
@@ -2727,8 +2962,11 @@
       <c r="G68" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>17</v>
       </c>
@@ -2750,8 +2988,11 @@
       <c r="G69" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>73</v>
       </c>
@@ -2773,8 +3014,11 @@
       <c r="G70" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>37</v>
       </c>
@@ -2796,8 +3040,11 @@
       <c r="G71" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>58</v>
       </c>
@@ -2819,8 +3066,11 @@
       <c r="G72" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>62</v>
       </c>
@@ -2842,8 +3092,11 @@
       <c r="G73" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>41</v>
       </c>
@@ -2865,8 +3118,11 @@
       <c r="G74" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>0</v>
       </c>
@@ -2888,8 +3144,11 @@
       <c r="G75" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>38</v>
       </c>
@@ -2910,6 +3169,9 @@
       </c>
       <c r="G76" t="s">
         <v>162</v>
+      </c>
+      <c r="H76" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2917,5 +3179,6 @@
     <sortCondition ref="E1:E76"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/output/cluster_review_edits.xlsx
+++ b/output/cluster_review_edits.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilya/spatial-queries/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A4460B-3118-6749-82E5-D09FE017C545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC77736A-69E3-FC46-8743-37BA40F7AB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24640" yWindow="620" windowWidth="25620" windowHeight="26900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="239">
   <si>
     <t>label</t>
   </si>
@@ -523,12 +536,6 @@
     <t>County membership of towns and places in US</t>
   </si>
   <si>
-    <t>Absolute locations of places</t>
-  </si>
-  <si>
-    <t>Best time to visit</t>
-  </si>
-  <si>
     <t>Contact details</t>
   </si>
   <si>
@@ -556,21 +563,9 @@
     <t>Legal status or eligibility</t>
   </si>
   <si>
-    <t>Casinos, resorts</t>
-  </si>
-  <si>
-    <t>Volcanoes</t>
-  </si>
-  <si>
     <t>Rivers</t>
   </si>
   <si>
-    <t>Mountains and landforms</t>
-  </si>
-  <si>
-    <t>Buildings and monuments</t>
-  </si>
-  <si>
     <t>Countries and regions in Africa</t>
   </si>
   <si>
@@ -631,12 +626,6 @@
     <t>Which province (Canada)</t>
   </si>
   <si>
-    <t>Sale locations</t>
-  </si>
-  <si>
-    <t>City/state comparisons</t>
-  </si>
-  <si>
     <t>Store locations and counts</t>
   </si>
   <si>
@@ -715,9 +704,6 @@
     <t>Generic factual queries</t>
   </si>
   <si>
-    <t>Distance and proximity</t>
-  </si>
-  <si>
     <t>Occurrence</t>
   </si>
   <si>
@@ -725,13 +711,52 @@
   </si>
   <si>
     <t>group</t>
+  </si>
+  <si>
+    <t>Referencing</t>
+  </si>
+  <si>
+    <t>Relations</t>
+  </si>
+  <si>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>group0</t>
+  </si>
+  <si>
+    <t>Best time or season to visit</t>
+  </si>
+  <si>
+    <t>Product sale locations</t>
+  </si>
+  <si>
+    <t>Rankings and comparisons of places</t>
+  </si>
+  <si>
+    <t>Buildings, monuments (height, location)</t>
+  </si>
+  <si>
+    <t>Mountains, landforms (elevation)</t>
+  </si>
+  <si>
+    <t>Temporal = Spatio-Temporal Qualification, treat as spatial attributes</t>
+  </si>
+  <si>
+    <t>Countries and cities (worldwide)</t>
+  </si>
+  <si>
+    <t>UNIQUE VALUES</t>
+  </si>
+  <si>
+    <t>Location and capactiy of casinos, resorts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -753,8 +778,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -776,6 +816,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -818,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -831,10 +877,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1137,7 +1186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="49.83203125" customWidth="1"/>
@@ -1145,12 +1194,13 @@
     <col min="5" max="5" width="67.83203125" customWidth="1"/>
     <col min="6" max="6" width="23.83203125" customWidth="1"/>
     <col min="7" max="7" width="23.33203125" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="53.6640625" customWidth="1"/>
-    <col min="10" max="10" width="37.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="53.6640625" customWidth="1"/>
+    <col min="11" max="11" width="37.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1164,7 +1214,7 @@
         <v>81</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>78</v>
@@ -1172,11 +1222,14 @@
       <c r="G1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H1" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>70</v>
       </c>
@@ -1187,7 +1240,7 @@
         <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="E2" t="s">
         <v>151</v>
@@ -1201,8 +1254,11 @@
       <c r="H2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>44</v>
       </c>
@@ -1213,22 +1269,25 @@
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="E3" t="s">
         <v>125</v>
       </c>
       <c r="F3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G3" t="s">
         <v>165</v>
       </c>
       <c r="H3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="I3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>36</v>
       </c>
@@ -1239,7 +1298,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
         <v>117</v>
@@ -1253,11 +1312,14 @@
       <c r="H4" t="s">
         <v>155</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>228</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1268,7 +1330,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
         <v>83</v>
@@ -1280,13 +1342,16 @@
         <v>161</v>
       </c>
       <c r="H5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="I5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1297,7 +1362,7 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
         <v>93</v>
@@ -1311,11 +1376,14 @@
       <c r="H6" t="s">
         <v>156</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>226</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>40</v>
       </c>
@@ -1326,7 +1394,7 @@
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
         <v>121</v>
@@ -1340,11 +1408,14 @@
       <c r="H7" t="s">
         <v>156</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>31</v>
       </c>
@@ -1355,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
         <v>112</v>
@@ -1369,11 +1440,14 @@
       <c r="H8" t="s">
         <v>156</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>27</v>
       </c>
@@ -1384,7 +1458,7 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E9" t="s">
         <v>108</v>
@@ -1398,11 +1472,14 @@
       <c r="H9" t="s">
         <v>156</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>47</v>
       </c>
@@ -1413,7 +1490,7 @@
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -1427,11 +1504,14 @@
       <c r="H10" t="s">
         <v>156</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>226</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>21</v>
       </c>
@@ -1442,7 +1522,7 @@
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E11" t="s">
         <v>101</v>
@@ -1456,11 +1536,14 @@
       <c r="H11" t="s">
         <v>156</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>226</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>28</v>
       </c>
@@ -1471,7 +1554,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
         <v>109</v>
@@ -1485,8 +1568,11 @@
       <c r="H12" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>53</v>
       </c>
@@ -1497,7 +1583,7 @@
         <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
         <v>134</v>
@@ -1511,8 +1597,11 @@
       <c r="H13" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>50</v>
       </c>
@@ -1523,7 +1612,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E14" t="s">
         <v>131</v>
@@ -1537,8 +1626,11 @@
       <c r="H14" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>30</v>
       </c>
@@ -1549,7 +1641,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
         <v>111</v>
@@ -1563,8 +1655,11 @@
       <c r="H15" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>19</v>
       </c>
@@ -1575,7 +1670,7 @@
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E16" t="s">
         <v>99</v>
@@ -1589,8 +1684,11 @@
       <c r="H16" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>18</v>
       </c>
@@ -1601,7 +1699,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E17" t="s">
         <v>98</v>
@@ -1615,8 +1713,11 @@
       <c r="H17" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I17" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>10</v>
       </c>
@@ -1627,7 +1728,7 @@
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
         <v>91</v>
@@ -1641,8 +1742,11 @@
       <c r="H18" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1653,7 +1757,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
         <v>95</v>
@@ -1667,8 +1771,11 @@
       <c r="H19" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>33</v>
       </c>
@@ -1679,7 +1786,7 @@
         <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
         <v>114</v>
@@ -1693,11 +1800,14 @@
       <c r="H20" t="s">
         <v>156</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I20" t="s">
+        <v>226</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>29</v>
       </c>
@@ -1708,7 +1818,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
         <v>110</v>
@@ -1722,11 +1832,14 @@
       <c r="H21" t="s">
         <v>156</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I21" t="s">
+        <v>226</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>43</v>
       </c>
@@ -1737,7 +1850,7 @@
         <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
         <v>124</v>
@@ -1751,11 +1864,14 @@
       <c r="H22" t="s">
         <v>156</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I22" t="s">
+        <v>226</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>45</v>
       </c>
@@ -1766,7 +1882,7 @@
         <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E23" t="s">
         <v>126</v>
@@ -1780,11 +1896,14 @@
       <c r="H23" t="s">
         <v>156</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I23" t="s">
+        <v>226</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>34</v>
       </c>
@@ -1795,7 +1914,7 @@
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E24" t="s">
         <v>115</v>
@@ -1809,11 +1928,14 @@
       <c r="H24" t="s">
         <v>156</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I24" t="s">
+        <v>226</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>52</v>
       </c>
@@ -1824,7 +1946,7 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E25" t="s">
         <v>133</v>
@@ -1838,11 +1960,14 @@
       <c r="H25" t="s">
         <v>156</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I25" t="s">
+        <v>226</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>13</v>
       </c>
@@ -1853,7 +1978,7 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
         <v>94</v>
@@ -1867,8 +1992,11 @@
       <c r="H26" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I26" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>42</v>
       </c>
@@ -1879,7 +2007,7 @@
         <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E27" t="s">
         <v>123</v>
@@ -1893,8 +2021,11 @@
       <c r="H27" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>32</v>
       </c>
@@ -1905,7 +2036,7 @@
         <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E28" t="s">
         <v>113</v>
@@ -1919,8 +2050,11 @@
       <c r="H28" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I28" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>25</v>
       </c>
@@ -1931,7 +2065,7 @@
         <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E29" t="s">
         <v>107</v>
@@ -1945,8 +2079,11 @@
       <c r="H29" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I29" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>26</v>
       </c>
@@ -1957,7 +2094,7 @@
         <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E30" t="s">
         <v>166</v>
@@ -1971,8 +2108,11 @@
       <c r="H30" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I30" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>68</v>
       </c>
@@ -1983,7 +2123,7 @@
         <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E31" t="s">
         <v>149</v>
@@ -1995,13 +2135,16 @@
         <v>162</v>
       </c>
       <c r="H31" t="s">
-        <v>231</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="I31" t="s">
+        <v>227</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>61</v>
       </c>
@@ -2012,7 +2155,7 @@
         <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
         <v>141</v>
@@ -2024,13 +2167,16 @@
         <v>162</v>
       </c>
       <c r="H32" t="s">
-        <v>231</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="I32" t="s">
+        <v>227</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>67</v>
       </c>
@@ -2041,7 +2187,7 @@
         <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
         <v>148</v>
@@ -2053,13 +2199,16 @@
         <v>162</v>
       </c>
       <c r="H33" t="s">
-        <v>231</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="I33" t="s">
+        <v>227</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>4</v>
       </c>
@@ -2070,7 +2219,7 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
         <v>86</v>
@@ -2082,13 +2231,16 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>231</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="I34" t="s">
+        <v>226</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>20</v>
       </c>
@@ -2113,11 +2265,14 @@
       <c r="H35" t="s">
         <v>155</v>
       </c>
-      <c r="I35" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I35" t="s">
+        <v>226</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>69</v>
       </c>
@@ -2128,7 +2283,7 @@
         <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
         <v>150</v>
@@ -2140,10 +2295,13 @@
         <v>165</v>
       </c>
       <c r="H36" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="I36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>-1</v>
       </c>
@@ -2154,13 +2312,13 @@
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E37" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>56</v>
       </c>
@@ -2171,7 +2329,7 @@
         <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E38" t="s">
         <v>137</v>
@@ -2183,10 +2341,16 @@
         <v>160</v>
       </c>
       <c r="H38" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="I38" t="s">
+        <v>158</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>63</v>
       </c>
@@ -2197,7 +2361,7 @@
         <v>67</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
         <v>142</v>
@@ -2209,10 +2373,16 @@
         <v>165</v>
       </c>
       <c r="H39" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="I39" t="s">
+        <v>158</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2</v>
       </c>
@@ -2223,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
         <v>84</v>
@@ -2237,8 +2407,14 @@
       <c r="H40" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I40" t="s">
+        <v>228</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>54</v>
       </c>
@@ -2249,7 +2425,7 @@
         <v>58</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="E41" t="s">
         <v>135</v>
@@ -2263,8 +2439,14 @@
       <c r="H41" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I41" t="s">
+        <v>228</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>48</v>
       </c>
@@ -2275,7 +2457,7 @@
         <v>52</v>
       </c>
       <c r="D42" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="E42" t="s">
         <v>129</v>
@@ -2289,8 +2471,14 @@
       <c r="H42" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I42" t="s">
+        <v>228</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>46</v>
       </c>
@@ -2301,7 +2489,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E43" t="s">
         <v>127</v>
@@ -2315,8 +2503,11 @@
       <c r="H43" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I43" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>35</v>
       </c>
@@ -2327,7 +2518,7 @@
         <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>234</v>
       </c>
       <c r="E44" t="s">
         <v>116</v>
@@ -2341,8 +2532,11 @@
       <c r="H44" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>9</v>
       </c>
@@ -2353,13 +2547,13 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="E45" t="s">
         <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G45" t="s">
         <v>160</v>
@@ -2367,8 +2561,11 @@
       <c r="H45" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I45" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>5</v>
       </c>
@@ -2379,7 +2576,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E46" t="s">
         <v>87</v>
@@ -2391,10 +2588,13 @@
         <v>164</v>
       </c>
       <c r="H46" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="I46" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>64</v>
       </c>
@@ -2405,7 +2605,7 @@
         <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
         <v>145</v>
@@ -2419,8 +2619,11 @@
       <c r="H47" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I47" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -2431,7 +2634,7 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E48" t="s">
         <v>106</v>
@@ -2445,8 +2648,11 @@
       <c r="H48" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>22</v>
       </c>
@@ -2457,7 +2663,7 @@
         <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s">
         <v>102</v>
@@ -2471,8 +2677,11 @@
       <c r="H49" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>55</v>
       </c>
@@ -2483,7 +2692,7 @@
         <v>59</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E50" t="s">
         <v>136</v>
@@ -2497,8 +2706,11 @@
       <c r="H50" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I50" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>60</v>
       </c>
@@ -2509,7 +2721,7 @@
         <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E51" t="s">
         <v>144</v>
@@ -2523,8 +2735,11 @@
       <c r="H51" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>3</v>
       </c>
@@ -2535,7 +2750,7 @@
         <v>7</v>
       </c>
       <c r="D52" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E52" t="s">
         <v>85</v>
@@ -2549,8 +2764,11 @@
       <c r="H52" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I52" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>15</v>
       </c>
@@ -2561,7 +2779,7 @@
         <v>19</v>
       </c>
       <c r="D53" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
         <v>96</v>
@@ -2575,8 +2793,11 @@
       <c r="H53" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I53" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>59</v>
       </c>
@@ -2587,7 +2808,7 @@
         <v>63</v>
       </c>
       <c r="D54" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E54" t="s">
         <v>143</v>
@@ -2601,8 +2822,11 @@
       <c r="H54" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>16</v>
       </c>
@@ -2613,7 +2837,7 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
         <v>105</v>
@@ -2627,8 +2851,11 @@
       <c r="H55" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>65</v>
       </c>
@@ -2639,7 +2866,7 @@
         <v>69</v>
       </c>
       <c r="D56" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
         <v>146</v>
@@ -2653,8 +2880,11 @@
       <c r="H56" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I56" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -2665,7 +2895,7 @@
         <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E57" t="s">
         <v>104</v>
@@ -2679,8 +2909,11 @@
       <c r="H57" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I57" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>23</v>
       </c>
@@ -2691,7 +2924,7 @@
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E58" t="s">
         <v>103</v>
@@ -2705,8 +2938,11 @@
       <c r="H58" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I58" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>49</v>
       </c>
@@ -2717,7 +2953,7 @@
         <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E59" t="s">
         <v>130</v>
@@ -2731,8 +2967,11 @@
       <c r="H59" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I59" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>11</v>
       </c>
@@ -2743,13 +2982,13 @@
         <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E60" t="s">
         <v>92</v>
       </c>
       <c r="F60" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G60" t="s">
         <v>160</v>
@@ -2757,8 +2996,11 @@
       <c r="H60" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I60" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>71</v>
       </c>
@@ -2769,7 +3011,7 @@
         <v>75</v>
       </c>
       <c r="D61" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E61" t="s">
         <v>152</v>
@@ -2783,8 +3025,11 @@
       <c r="H61" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I61" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>66</v>
       </c>
@@ -2795,7 +3040,7 @@
         <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E62" t="s">
         <v>147</v>
@@ -2809,8 +3054,11 @@
       <c r="H62" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I62" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>51</v>
       </c>
@@ -2821,7 +3069,7 @@
         <v>55</v>
       </c>
       <c r="D63" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E63" t="s">
         <v>132</v>
@@ -2833,10 +3081,13 @@
         <v>163</v>
       </c>
       <c r="H63" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="I63" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>57</v>
       </c>
@@ -2847,22 +3098,25 @@
         <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E64" t="s">
         <v>138</v>
       </c>
       <c r="F64" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G64" t="s">
         <v>161</v>
       </c>
       <c r="H64" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="I64" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>6</v>
       </c>
@@ -2873,7 +3127,7 @@
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E65" t="s">
         <v>88</v>
@@ -2887,8 +3141,11 @@
       <c r="H65" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I65" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>39</v>
       </c>
@@ -2899,13 +3156,13 @@
         <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E66" t="s">
         <v>120</v>
       </c>
       <c r="F66" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G66" t="s">
         <v>162</v>
@@ -2913,8 +3170,11 @@
       <c r="H66" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I66" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>7</v>
       </c>
@@ -2925,7 +3185,7 @@
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E67" t="s">
         <v>89</v>
@@ -2939,8 +3199,11 @@
       <c r="H67" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I67" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>72</v>
       </c>
@@ -2951,7 +3214,7 @@
         <v>76</v>
       </c>
       <c r="D68" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="E68" t="s">
         <v>153</v>
@@ -2965,8 +3228,11 @@
       <c r="H68" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I68" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>17</v>
       </c>
@@ -2977,13 +3243,13 @@
         <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="E69" t="s">
         <v>97</v>
       </c>
       <c r="F69" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G69" t="s">
         <v>162</v>
@@ -2991,8 +3257,11 @@
       <c r="H69" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I69" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>73</v>
       </c>
@@ -3003,7 +3272,7 @@
         <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E70" t="s">
         <v>154</v>
@@ -3017,8 +3286,11 @@
       <c r="H70" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I70" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>37</v>
       </c>
@@ -3029,7 +3301,7 @@
         <v>41</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E71" t="s">
         <v>118</v>
@@ -3043,8 +3315,11 @@
       <c r="H71" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I71" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>58</v>
       </c>
@@ -3055,22 +3330,25 @@
         <v>62</v>
       </c>
       <c r="D72" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E72" t="s">
         <v>139</v>
       </c>
       <c r="F72" t="s">
+        <v>216</v>
+      </c>
+      <c r="G72" t="s">
+        <v>162</v>
+      </c>
+      <c r="H72" t="s">
         <v>224</v>
       </c>
-      <c r="G72" t="s">
-        <v>162</v>
-      </c>
-      <c r="H72" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I72" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>62</v>
       </c>
@@ -3092,11 +3370,14 @@
       <c r="G73" t="s">
         <v>162</v>
       </c>
-      <c r="H73" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H73" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>41</v>
       </c>
@@ -3107,22 +3388,25 @@
         <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E74" t="s">
         <v>122</v>
       </c>
       <c r="F74" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G74" t="s">
         <v>163</v>
       </c>
       <c r="H74" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="I74" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>0</v>
       </c>
@@ -3133,22 +3417,25 @@
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E75" t="s">
         <v>82</v>
       </c>
       <c r="F75" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G75" t="s">
         <v>160</v>
       </c>
       <c r="H75" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="I75" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>38</v>
       </c>
@@ -3159,7 +3446,7 @@
         <v>42</v>
       </c>
       <c r="D76" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E76" t="s">
         <v>119</v>
@@ -3172,6 +3459,22 @@
       </c>
       <c r="H76" t="s">
         <v>156</v>
+      </c>
+      <c r="I76" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C82" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D82" s="10">
+        <f>COUNTA(_xlfn.UNIQUE(D2:D76))</f>
+        <v>48</v>
+      </c>
+      <c r="E82" s="10">
+        <f>COUNTA(_xlfn.UNIQUE(E2:E76))</f>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
